--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/oct-2025.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/oct-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC oct-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC oct-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/oct-2025.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/oct-2025.xlsx
@@ -562,7 +562,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -810,7 +818,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -871,7 +883,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -932,7 +948,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1054,7 +1074,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1115,7 +1139,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1241,7 +1269,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1302,7 +1334,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1363,7 +1399,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1424,7 +1464,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1550,7 +1594,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1672,7 +1720,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1733,7 +1785,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1859,7 +1915,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1920,7 +1980,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1981,7 +2045,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2042,7 +2110,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2103,7 +2175,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2164,7 +2240,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2286,7 +2366,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2347,7 +2431,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2408,7 +2496,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2469,7 +2561,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2591,7 +2687,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2713,7 +2813,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2774,7 +2878,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2835,7 +2943,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2896,7 +3008,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3022,7 +3138,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3144,7 +3264,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3205,7 +3329,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3266,7 +3394,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3327,7 +3459,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3388,7 +3524,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3449,7 +3589,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3510,7 +3654,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3571,7 +3719,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3632,7 +3784,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3693,7 +3849,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3754,7 +3914,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3945,7 +4109,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4006,7 +4174,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4067,7 +4239,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4128,7 +4304,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4311,7 +4491,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4433,7 +4617,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4494,7 +4682,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4555,7 +4747,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4616,7 +4812,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
